--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4D499A-1B86-43FC-B552-B6195F137374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390646DE-93DA-4F2B-81F2-1CEC457BEA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 24.10.2025</t>
-  </si>
-  <si>
     <t>Relatório de Recusa SICOOB 27.10.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 27.10.2025</t>
   </si>
 </sst>
 </file>
@@ -537,10 +537,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -554,10 +554,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -571,10 +571,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -598,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390646DE-93DA-4F2B-81F2-1CEC457BEA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65BE3FC-6CC7-4FAE-A9BD-710D1BADB4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,17 +54,38 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 27.10.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 27.10.2025</t>
+    <t>135047185</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 28.10.2025</t>
+  </si>
+  <si>
+    <t>132092294</t>
+  </si>
+  <si>
+    <t>135130311</t>
+  </si>
+  <si>
+    <t>134926015</t>
+  </si>
+  <si>
+    <t>135025219</t>
+  </si>
+  <si>
+    <t>135018750</t>
+  </si>
+  <si>
+    <t>135063352</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 28.10.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,12 +106,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -113,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -121,26 +136,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -157,36 +157,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -499,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -530,63 +505,127 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>135064587</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>8</v>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>134924586</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>134948391</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -598,31 +637,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65BE3FC-6CC7-4FAE-A9BD-710D1BADB4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC192C1D-FAE7-413A-9301-E0F0C3302117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>135047185</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 28.10.2025</t>
-  </si>
-  <si>
-    <t>132092294</t>
-  </si>
-  <si>
-    <t>135130311</t>
-  </si>
-  <si>
-    <t>134926015</t>
-  </si>
-  <si>
-    <t>135025219</t>
-  </si>
-  <si>
-    <t>135018750</t>
-  </si>
-  <si>
-    <t>135063352</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 28.10.2025</t>
+    <t>134875044</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 24.10.2025</t>
+  </si>
+  <si>
+    <t>135074734</t>
+  </si>
+  <si>
+    <t>134980797</t>
+  </si>
+  <si>
+    <t>134968908</t>
+  </si>
+  <si>
+    <t>134974393</t>
+  </si>
+  <si>
+    <t>133425615</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 24.10.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -532,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -549,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -583,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -600,26 +597,9 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -637,31 +617,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC192C1D-FAE7-413A-9301-E0F0C3302117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F67285-6866-4C5E-B093-9FAC45675E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,46 @@
     <t>971</t>
   </si>
   <si>
-    <t>134875044</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 24.10.2025</t>
-  </si>
-  <si>
-    <t>135074734</t>
-  </si>
-  <si>
-    <t>134980797</t>
-  </si>
-  <si>
-    <t>134968908</t>
-  </si>
-  <si>
-    <t>134974393</t>
-  </si>
-  <si>
-    <t>133425615</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.10.2025</t>
+    <t>134974965</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 29.10.2025</t>
+  </si>
+  <si>
+    <t>134983136</t>
+  </si>
+  <si>
+    <t>135073541</t>
+  </si>
+  <si>
+    <t>135092944</t>
+  </si>
+  <si>
+    <t>135094251</t>
+  </si>
+  <si>
+    <t>135099801</t>
+  </si>
+  <si>
+    <t>135097795</t>
+  </si>
+  <si>
+    <t>135120151</t>
+  </si>
+  <si>
+    <t>135134622</t>
+  </si>
+  <si>
+    <t>135058071</t>
+  </si>
+  <si>
+    <t>135159523</t>
+  </si>
+  <si>
+    <t>135054967</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 29.10.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +489,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -546,7 +564,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -563,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -580,7 +598,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,9 +615,111 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -617,31 +737,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F67285-6866-4C5E-B093-9FAC45675E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D484521-BBF7-45D6-9EEA-C9DDEA18E01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,46 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>134974965</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 29.10.2025</t>
-  </si>
-  <si>
     <t>134983136</t>
   </si>
   <si>
-    <t>135073541</t>
-  </si>
-  <si>
-    <t>135092944</t>
-  </si>
-  <si>
-    <t>135094251</t>
-  </si>
-  <si>
-    <t>135099801</t>
-  </si>
-  <si>
-    <t>135097795</t>
-  </si>
-  <si>
-    <t>135120151</t>
-  </si>
-  <si>
-    <t>135134622</t>
-  </si>
-  <si>
-    <t>135058071</t>
-  </si>
-  <si>
-    <t>135159523</t>
-  </si>
-  <si>
-    <t>135054967</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 29.10.2025</t>
+    <t>Relatório de Recusa SICOOB 30.10.2025</t>
+  </si>
+  <si>
+    <t>135047505</t>
+  </si>
+  <si>
+    <t>135059130</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 30.10.2025</t>
   </si>
 </sst>
 </file>
@@ -489,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -530,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -547,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -564,162 +537,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -737,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D484521-BBF7-45D6-9EEA-C9DDEA18E01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC9F8C3-FCBA-42B2-AD61-FD6C97CCB42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>134983136</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 30.10.2025</t>
-  </si>
-  <si>
-    <t>135047505</t>
-  </si>
-  <si>
-    <t>135059130</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 30.10.2025</t>
+    <t>135072802</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 31.10.2025</t>
+  </si>
+  <si>
+    <t>135097825</t>
+  </si>
+  <si>
+    <t>135121935</t>
+  </si>
+  <si>
+    <t>134950762</t>
+  </si>
+  <si>
+    <t>135177617</t>
+  </si>
+  <si>
+    <t>135094687</t>
+  </si>
+  <si>
+    <t>135191216</t>
+  </si>
+  <si>
+    <t>135057324</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 31.10.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,9 +552,94 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +657,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC9F8C3-FCBA-42B2-AD61-FD6C97CCB42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF2BA9-481F-4162-858E-9A16C7BC5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>135072802</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 31.10.2025</t>
-  </si>
-  <si>
-    <t>135097825</t>
-  </si>
-  <si>
-    <t>135121935</t>
-  </si>
-  <si>
-    <t>134950762</t>
-  </si>
-  <si>
-    <t>135177617</t>
-  </si>
-  <si>
-    <t>135094687</t>
-  </si>
-  <si>
-    <t>135191216</t>
-  </si>
-  <si>
-    <t>135057324</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 31.10.2025</t>
+    <t>134882383</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 03.11.2025</t>
+  </si>
+  <si>
+    <t>135159633</t>
+  </si>
+  <si>
+    <t>135150857</t>
+  </si>
+  <si>
+    <t>134524259</t>
+  </si>
+  <si>
+    <t>133885337</t>
+  </si>
+  <si>
+    <t>135133393</t>
+  </si>
+  <si>
+    <t>135217115</t>
+  </si>
+  <si>
+    <t>135133627</t>
+  </si>
+  <si>
+    <t>135056800</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 03.11.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -603,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -620,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -637,9 +640,26 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -657,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF2BA9-481F-4162-858E-9A16C7BC5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB8F969-D3AB-41B6-8DC1-8E6DD6C280B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>134882383</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 03.11.2025</t>
-  </si>
-  <si>
-    <t>135159633</t>
-  </si>
-  <si>
-    <t>135150857</t>
-  </si>
-  <si>
-    <t>134524259</t>
-  </si>
-  <si>
-    <t>133885337</t>
-  </si>
-  <si>
-    <t>135133393</t>
-  </si>
-  <si>
-    <t>135217115</t>
-  </si>
-  <si>
-    <t>135133627</t>
-  </si>
-  <si>
-    <t>135056800</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 03.11.2025</t>
+    <t>135158375</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 04.11.2025</t>
+  </si>
+  <si>
+    <t>135199703</t>
+  </si>
+  <si>
+    <t>135045608</t>
+  </si>
+  <si>
+    <t>135055434</t>
+  </si>
+  <si>
+    <t>135090228</t>
+  </si>
+  <si>
+    <t>130502761</t>
+  </si>
+  <si>
+    <t>135234650</t>
+  </si>
+  <si>
+    <t>135122357</t>
+  </si>
+  <si>
+    <t>135242648</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 04.11.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -580,7 +580,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -614,7 +614,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -648,18 +648,52 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -677,31 +711,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB8F969-D3AB-41B6-8DC1-8E6DD6C280B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A55C5-EBC2-43CE-80FF-D994C118AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>135158375</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 04.11.2025</t>
-  </si>
-  <si>
-    <t>135199703</t>
-  </si>
-  <si>
-    <t>135045608</t>
-  </si>
-  <si>
-    <t>135055434</t>
-  </si>
-  <si>
-    <t>135090228</t>
-  </si>
-  <si>
-    <t>130502761</t>
-  </si>
-  <si>
-    <t>135234650</t>
-  </si>
-  <si>
-    <t>135122357</t>
-  </si>
-  <si>
-    <t>135242648</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 04.11.2025</t>
+    <t>135185671</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 06.11.2025</t>
+  </si>
+  <si>
+    <t>135197921</t>
+  </si>
+  <si>
+    <t>135095904</t>
+  </si>
+  <si>
+    <t>135213186</t>
+  </si>
+  <si>
+    <t>135157373</t>
+  </si>
+  <si>
+    <t>135220506</t>
+  </si>
+  <si>
+    <t>135277900</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 06.11.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +549,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +566,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -580,7 +574,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -589,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,7 +591,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -606,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -614,7 +608,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -623,77 +617,9 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -711,31 +637,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2A55C5-EBC2-43CE-80FF-D994C118AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915C97C2-5463-468D-9F61-8E2593B1F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,58 @@
     <t>971</t>
   </si>
   <si>
-    <t>135185671</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 06.11.2025</t>
-  </si>
-  <si>
-    <t>135197921</t>
-  </si>
-  <si>
-    <t>135095904</t>
-  </si>
-  <si>
-    <t>135213186</t>
-  </si>
-  <si>
-    <t>135157373</t>
-  </si>
-  <si>
-    <t>135220506</t>
-  </si>
-  <si>
-    <t>135277900</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 06.11.2025</t>
+    <t>135165940</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 07.11.2025</t>
+  </si>
+  <si>
+    <t>135179437</t>
+  </si>
+  <si>
+    <t>135180053</t>
+  </si>
+  <si>
+    <t>135216734</t>
+  </si>
+  <si>
+    <t>135177532</t>
+  </si>
+  <si>
+    <t>135167253</t>
+  </si>
+  <si>
+    <t>135166355</t>
+  </si>
+  <si>
+    <t>135171984</t>
+  </si>
+  <si>
+    <t>135173309</t>
+  </si>
+  <si>
+    <t>132670683</t>
+  </si>
+  <si>
+    <t>135299730</t>
+  </si>
+  <si>
+    <t>135127500</t>
+  </si>
+  <si>
+    <t>133060865</t>
+  </si>
+  <si>
+    <t>135135090</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 07.11.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 08.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 08.11.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +501,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -532,7 +559,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -549,7 +576,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,7 +593,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -583,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -600,7 +627,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -617,9 +644,145 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915C97C2-5463-468D-9F61-8E2593B1F91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F607D-EF8B-4002-B0FB-F263FC32E472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,43 @@
     <t>971</t>
   </si>
   <si>
-    <t>135165940</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 07.11.2025</t>
-  </si>
-  <si>
-    <t>135179437</t>
-  </si>
-  <si>
-    <t>135180053</t>
-  </si>
-  <si>
-    <t>135216734</t>
-  </si>
-  <si>
-    <t>135177532</t>
-  </si>
-  <si>
-    <t>135167253</t>
-  </si>
-  <si>
-    <t>135166355</t>
-  </si>
-  <si>
-    <t>135171984</t>
-  </si>
-  <si>
-    <t>135173309</t>
-  </si>
-  <si>
-    <t>132670683</t>
-  </si>
-  <si>
-    <t>135299730</t>
-  </si>
-  <si>
-    <t>135127500</t>
-  </si>
-  <si>
-    <t>133060865</t>
-  </si>
-  <si>
-    <t>135135090</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 07.11.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 08.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 08.11.2025</t>
+    <t>135200116</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 10.11.2025</t>
+  </si>
+  <si>
+    <t>135228178</t>
+  </si>
+  <si>
+    <t>135256344</t>
+  </si>
+  <si>
+    <t>135275622</t>
+  </si>
+  <si>
+    <t>135281368</t>
+  </si>
+  <si>
+    <t>135306989</t>
+  </si>
+  <si>
+    <t>135212572</t>
+  </si>
+  <si>
+    <t>135193876</t>
+  </si>
+  <si>
+    <t>131282282</t>
+  </si>
+  <si>
+    <t>135197064</t>
+  </si>
+  <si>
+    <t>135200592</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 10.11.2025</t>
   </si>
 </sst>
 </file>
@@ -501,7 +486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -542,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -559,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -576,7 +561,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -593,7 +578,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -610,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -627,7 +612,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -644,7 +629,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -661,7 +646,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -678,7 +663,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -695,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -712,77 +697,9 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -800,31 +717,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0F607D-EF8B-4002-B0FB-F263FC32E472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50DBD23-5307-4A1E-B78E-848529F26F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,43 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>135200116</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 10.11.2025</t>
-  </si>
-  <si>
-    <t>135228178</t>
-  </si>
-  <si>
-    <t>135256344</t>
-  </si>
-  <si>
-    <t>135275622</t>
-  </si>
-  <si>
-    <t>135281368</t>
-  </si>
-  <si>
-    <t>135306989</t>
-  </si>
-  <si>
-    <t>135212572</t>
-  </si>
-  <si>
-    <t>135193876</t>
-  </si>
-  <si>
-    <t>131282282</t>
-  </si>
-  <si>
-    <t>135197064</t>
-  </si>
-  <si>
-    <t>135200592</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 10.11.2025</t>
+    <t>135253573</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 11.11.2025</t>
+  </si>
+  <si>
+    <t>135231429</t>
+  </si>
+  <si>
+    <t>133455912</t>
+  </si>
+  <si>
+    <t>133926729</t>
+  </si>
+  <si>
+    <t>135338811</t>
+  </si>
+  <si>
+    <t>135342995</t>
+  </si>
+  <si>
+    <t>135201307</t>
+  </si>
+  <si>
+    <t>135170271</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 11.11.2025</t>
   </si>
 </sst>
 </file>
@@ -486,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -527,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -544,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -561,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -578,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -595,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -612,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -629,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -646,60 +637,9 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -717,31 +657,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50DBD23-5307-4A1E-B78E-848529F26F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A273C86B-4966-4FD3-8054-6EC1D9AB0785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,34 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>135253573</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 11.11.2025</t>
-  </si>
-  <si>
-    <t>135231429</t>
-  </si>
-  <si>
-    <t>133455912</t>
-  </si>
-  <si>
-    <t>133926729</t>
-  </si>
-  <si>
-    <t>135338811</t>
-  </si>
-  <si>
-    <t>135342995</t>
-  </si>
-  <si>
-    <t>135201307</t>
-  </si>
-  <si>
-    <t>135170271</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 11.11.2025</t>
+    <t>135277078</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 12.11.2025</t>
+  </si>
+  <si>
+    <t>135268999</t>
+  </si>
+  <si>
+    <t>132670683</t>
+  </si>
+  <si>
+    <t>135348441</t>
+  </si>
+  <si>
+    <t>135353872</t>
+  </si>
+  <si>
+    <t>135358746</t>
+  </si>
+  <si>
+    <t>135359376</t>
+  </si>
+  <si>
+    <t>135297446</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 12.11.2025</t>
   </si>
 </sst>
 </file>
@@ -657,31 +657,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A273C86B-4966-4FD3-8054-6EC1D9AB0785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D183F11-8548-44B8-A50F-1EDAA49370B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,40 @@
     <t>971</t>
   </si>
   <si>
-    <t>135277078</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 12.11.2025</t>
-  </si>
-  <si>
-    <t>135268999</t>
-  </si>
-  <si>
-    <t>132670683</t>
-  </si>
-  <si>
-    <t>135348441</t>
-  </si>
-  <si>
-    <t>135353872</t>
-  </si>
-  <si>
-    <t>135358746</t>
-  </si>
-  <si>
-    <t>135359376</t>
-  </si>
-  <si>
-    <t>135297446</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 12.11.2025</t>
+    <t>135230693</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 15.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 15.11.2025</t>
+  </si>
+  <si>
+    <t>135327585</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 14.11.2025</t>
+  </si>
+  <si>
+    <t>135331373</t>
+  </si>
+  <si>
+    <t>135329099</t>
+  </si>
+  <si>
+    <t>135342178</t>
+  </si>
+  <si>
+    <t>135342214</t>
+  </si>
+  <si>
+    <t>135385203</t>
+  </si>
+  <si>
+    <t>135306899</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 14.11.2025</t>
   </si>
 </sst>
 </file>
@@ -518,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,16 +532,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,16 +549,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,16 +566,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,16 +583,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -594,16 +600,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -611,16 +617,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -628,16 +634,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D183F11-8548-44B8-A50F-1EDAA49370B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C92FF4-DF60-4BF4-A097-2C6D0B660E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>135230693</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 15.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 15.11.2025</t>
-  </si>
-  <si>
-    <t>135327585</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 14.11.2025</t>
-  </si>
-  <si>
-    <t>135331373</t>
-  </si>
-  <si>
-    <t>135329099</t>
-  </si>
-  <si>
-    <t>135342178</t>
-  </si>
-  <si>
-    <t>135342214</t>
-  </si>
-  <si>
-    <t>135385203</t>
-  </si>
-  <si>
-    <t>135306899</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 14.11.2025</t>
+    <t>135342263</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 17.11.2025</t>
+  </si>
+  <si>
+    <t>135369945</t>
+  </si>
+  <si>
+    <t>131689497</t>
+  </si>
+  <si>
+    <t>135320632</t>
+  </si>
+  <si>
+    <t>132022115</t>
+  </si>
+  <si>
+    <t>135269910</t>
+  </si>
+  <si>
+    <t>135270727</t>
+  </si>
+  <si>
+    <t>135282610</t>
+  </si>
+  <si>
+    <t>135292454</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 17.11.2025</t>
   </si>
 </sst>
 </file>
@@ -483,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -524,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -532,16 +529,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -549,16 +546,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,16 +563,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -583,16 +580,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -600,16 +597,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -617,16 +614,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -634,18 +631,35 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -663,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C92FF4-DF60-4BF4-A097-2C6D0B660E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65DE75-1E0B-484C-862F-FAB35F6C8159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>135342263</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 17.11.2025</t>
-  </si>
-  <si>
-    <t>135369945</t>
-  </si>
-  <si>
-    <t>131689497</t>
-  </si>
-  <si>
-    <t>135320632</t>
-  </si>
-  <si>
-    <t>132022115</t>
-  </si>
-  <si>
-    <t>135269910</t>
-  </si>
-  <si>
-    <t>135270727</t>
-  </si>
-  <si>
-    <t>135282610</t>
-  </si>
-  <si>
-    <t>135292454</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 17.11.2025</t>
+    <t>135409074</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.11.2025</t>
+  </si>
+  <si>
+    <t>135448832</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,128 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -677,31 +537,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65DE75-1E0B-484C-862F-FAB35F6C8159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C366A3-6755-47AA-A55D-F5B27B7A5210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,31 +537,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C366A3-6755-47AA-A55D-F5B27B7A5210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81360D17-9FB1-4626-8A69-AFAC7297DF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -537,31 +537,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81360D17-9FB1-4626-8A69-AFAC7297DF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C04F9F7-CAA1-4F11-A7C1-7595358B1E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,61 @@
     <t>971</t>
   </si>
   <si>
-    <t>135409074</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 18.11.2025</t>
-  </si>
-  <si>
-    <t>135448832</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 18.11.2025</t>
+    <t>135352291</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 19.11.2025</t>
+  </si>
+  <si>
+    <t>135370346</t>
+  </si>
+  <si>
+    <t>135397882</t>
+  </si>
+  <si>
+    <t>135419107</t>
+  </si>
+  <si>
+    <t>135309537</t>
+  </si>
+  <si>
+    <t>135475736</t>
+  </si>
+  <si>
+    <t>135386173</t>
+  </si>
+  <si>
+    <t>131322144</t>
+  </si>
+  <si>
+    <t>135308797</t>
+  </si>
+  <si>
+    <t>135325557</t>
+  </si>
+  <si>
+    <t>135330994</t>
+  </si>
+  <si>
+    <t>135356620</t>
+  </si>
+  <si>
+    <t>135362184</t>
+  </si>
+  <si>
+    <t>135362275</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 19.11.2025</t>
+  </si>
+  <si>
+    <t>135448776</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 20.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 20.11.2025</t>
   </si>
 </sst>
 </file>
@@ -459,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,9 +562,230 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -537,31 +803,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C04F9F7-CAA1-4F11-A7C1-7595358B1E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F9184-875C-4D25-B746-A5033CB69829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,31 +803,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F9184-875C-4D25-B746-A5033CB69829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8094E-4039-43F7-86BF-39EF39B39270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,68 +54,17 @@
     <t>971</t>
   </si>
   <si>
-    <t>135352291</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 19.11.2025</t>
-  </si>
-  <si>
-    <t>135370346</t>
-  </si>
-  <si>
-    <t>135397882</t>
-  </si>
-  <si>
-    <t>135419107</t>
-  </si>
-  <si>
-    <t>135309537</t>
-  </si>
-  <si>
-    <t>135475736</t>
-  </si>
-  <si>
-    <t>135386173</t>
-  </si>
-  <si>
-    <t>131322144</t>
-  </si>
-  <si>
-    <t>135308797</t>
-  </si>
-  <si>
-    <t>135325557</t>
-  </si>
-  <si>
-    <t>135330994</t>
-  </si>
-  <si>
-    <t>135356620</t>
-  </si>
-  <si>
-    <t>135362184</t>
-  </si>
-  <si>
-    <t>135362275</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 19.11.2025</t>
-  </si>
-  <si>
-    <t>135448776</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 20.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 20.11.2025</t>
+    <t>Relatório de Recusa SICOOB 21.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 21.11.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +85,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -158,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,11 +121,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -187,11 +157,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -504,7 +497,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -535,263 +528,46 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6">
+        <v>135445233</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="6">
+        <v>135404263</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A3">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8094E-4039-43F7-86BF-39EF39B39270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175603EC-00AF-40EE-BA66-5AE699D3F805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,10 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 21.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 21.11.2025</t>
+    <t>Relatório de Recusa SICOOB 24.11.2025</t>
+  </si>
+  <si>
+    <t>135489608</t>
+  </si>
+  <si>
+    <t>135342285</t>
+  </si>
+  <si>
+    <t>135400913</t>
+  </si>
+  <si>
+    <t>135409664</t>
+  </si>
+  <si>
+    <t>135411195</t>
+  </si>
+  <si>
+    <t>135411243</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 24.11.2025</t>
   </si>
 </sst>
 </file>
@@ -497,7 +515,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -529,7 +547,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135445233</v>
+        <v>135394646</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -538,7 +556,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -546,7 +564,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135404263</v>
+        <v>135466682</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -555,9 +573,111 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -579,31 +699,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175603EC-00AF-40EE-BA66-5AE699D3F805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9AF306-0204-484C-B5D7-E52F2508748C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 24.11.2025</t>
-  </si>
-  <si>
-    <t>135489608</t>
-  </si>
-  <si>
-    <t>135342285</t>
-  </si>
-  <si>
-    <t>135400913</t>
-  </si>
-  <si>
-    <t>135409664</t>
-  </si>
-  <si>
-    <t>135411195</t>
-  </si>
-  <si>
-    <t>135411243</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.11.2025</t>
+    <t>Relatório de Recusa SICOOB 25.11.2025</t>
+  </si>
+  <si>
+    <t>135448112</t>
+  </si>
+  <si>
+    <t>135477507</t>
+  </si>
+  <si>
+    <t>135517429</t>
+  </si>
+  <si>
+    <t>135531298</t>
+  </si>
+  <si>
+    <t>135541616</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 25.11.2025</t>
   </si>
 </sst>
 </file>
@@ -515,7 +512,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -547,7 +544,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135394646</v>
+        <v>135370990</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -556,7 +553,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -564,7 +561,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135466682</v>
+        <v>135355566</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -573,7 +570,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -590,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -607,7 +604,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -624,7 +621,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -641,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -658,26 +655,9 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -699,31 +679,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9AF306-0204-484C-B5D7-E52F2508748C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540F7194-AF68-4347-8FE3-393A7F55199E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 25.11.2025</t>
-  </si>
-  <si>
-    <t>135448112</t>
-  </si>
-  <si>
-    <t>135477507</t>
-  </si>
-  <si>
-    <t>135517429</t>
-  </si>
-  <si>
-    <t>135531298</t>
-  </si>
-  <si>
-    <t>135541616</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 25.11.2025</t>
+    <t>Relatório de Recusa SICOOB 26.11.2025</t>
+  </si>
+  <si>
+    <t>135510841</t>
+  </si>
+  <si>
+    <t>135541743</t>
+  </si>
+  <si>
+    <t>135421866</t>
+  </si>
+  <si>
+    <t>135381718</t>
+  </si>
+  <si>
+    <t>135495438</t>
+  </si>
+  <si>
+    <t>135562163</t>
+  </si>
+  <si>
+    <t>135491438</t>
+  </si>
+  <si>
+    <t>135468862</t>
+  </si>
+  <si>
+    <t>135466596</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 26.11.2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -544,7 +556,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135370990</v>
+        <v>135468862</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -553,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -561,7 +573,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135355566</v>
+        <v>135466596</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -570,7 +582,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -587,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -604,7 +616,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -621,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -638,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -655,9 +667,196 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -679,31 +878,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCB2AAA-7FB7-4A56-9C5E-D5F8112A9798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75539451-2654-4B65-A0D1-2B162323CE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,10 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 27.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 27.11.2025</t>
+    <t>Relatório de Recusa SICOOB 28.11.2025</t>
+  </si>
+  <si>
+    <t>131854427</t>
+  </si>
+  <si>
+    <t>135613667</t>
+  </si>
+  <si>
+    <t>135438565</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 28.11.2025</t>
+  </si>
+  <si>
+    <t>135442163</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 29.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 29.11.2025</t>
   </si>
 </sst>
 </file>
@@ -497,7 +515,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -529,7 +547,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135472753</v>
+        <v>135530631</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -538,7 +556,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -546,7 +564,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135423560</v>
+        <v>135601603</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -555,9 +573,77 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75539451-2654-4B65-A0D1-2B162323CE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A40EFC4-C6B8-4C41-83EF-8A3091D4B571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 28.11.2025</t>
-  </si>
-  <si>
-    <t>131854427</t>
-  </si>
-  <si>
-    <t>135613667</t>
-  </si>
-  <si>
-    <t>135438565</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 28.11.2025</t>
-  </si>
-  <si>
-    <t>135442163</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 29.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 29.11.2025</t>
+    <t>Relatório de Recusa SICOOB 01.12.2025</t>
+  </si>
+  <si>
+    <t>135638059</t>
+  </si>
+  <si>
+    <t>135638050</t>
+  </si>
+  <si>
+    <t>135497837</t>
+  </si>
+  <si>
+    <t>135498334</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 01.12.2025</t>
   </si>
 </sst>
 </file>
@@ -547,7 +541,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135530631</v>
+        <v>135561663</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -556,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -564,7 +558,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135601603</v>
+        <v>135626861</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -573,7 +567,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -590,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -607,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -624,7 +618,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -632,16 +626,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -665,31 +659,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A40EFC4-C6B8-4C41-83EF-8A3091D4B571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E52DA42-98D9-4658-96C0-569FB8283AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,10 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 01.12.2025</t>
-  </si>
-  <si>
-    <t>135638059</t>
-  </si>
-  <si>
-    <t>135638050</t>
-  </si>
-  <si>
-    <t>135497837</t>
-  </si>
-  <si>
-    <t>135498334</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 01.12.2025</t>
+    <t>Relatório de Recusa SICOOB 02.12.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 02.12.2025</t>
   </si>
 </sst>
 </file>
@@ -509,7 +497,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -541,7 +529,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135561663</v>
+        <v>135511805</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -550,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -558,7 +546,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135626861</v>
+        <v>135655236</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -567,77 +555,9 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -659,31 +579,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E52DA42-98D9-4658-96C0-569FB8283AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACFFAD4-AFD6-47C1-A520-4E4FEF4B69F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,10 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 02.12.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 02.12.2025</t>
+    <t>Relatório de Recusa SICOOB 03.12.2025</t>
+  </si>
+  <si>
+    <t>135662832</t>
+  </si>
+  <si>
+    <t>135672015</t>
+  </si>
+  <si>
+    <t>135682374</t>
+  </si>
+  <si>
+    <t>135686756</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 03.12.2025</t>
   </si>
 </sst>
 </file>
@@ -497,7 +509,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -529,7 +541,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135511805</v>
+        <v>135663471</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -538,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -546,7 +558,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135655236</v>
+        <v>135664662</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -555,9 +567,77 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -579,31 +659,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACFFAD4-AFD6-47C1-A520-4E4FEF4B69F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3917191F-15D7-42AF-9720-AA6E4AD82814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="885" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -54,22 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 03.12.2025</t>
-  </si>
-  <si>
-    <t>135662832</t>
-  </si>
-  <si>
-    <t>135672015</t>
-  </si>
-  <si>
-    <t>135682374</t>
-  </si>
-  <si>
-    <t>135686756</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 03.12.2025</t>
+    <t>Relatório de Recusa SICOOB 04.12.2025</t>
+  </si>
+  <si>
+    <t>135483673</t>
+  </si>
+  <si>
+    <t>135706784</t>
+  </si>
+  <si>
+    <t>135612309</t>
+  </si>
+  <si>
+    <t>134938248</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 04.12.2025</t>
   </si>
 </sst>
 </file>
@@ -541,7 +541,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135663471</v>
+        <v>135500230</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135664662</v>
+        <v>135487116</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -659,31 +659,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3917191F-15D7-42AF-9720-AA6E4AD82814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0878536E-84AA-4AE8-87C4-2BF2D8D0B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="885" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 04.12.2025</t>
-  </si>
-  <si>
-    <t>135483673</t>
-  </si>
-  <si>
-    <t>135706784</t>
-  </si>
-  <si>
-    <t>135612309</t>
-  </si>
-  <si>
-    <t>134938248</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 04.12.2025</t>
+    <t>Recusa Sicoob 06.12.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 06.12.2025</t>
+  </si>
+  <si>
+    <t>135547919</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 05.12.2025</t>
+  </si>
+  <si>
+    <t>135677574</t>
+  </si>
+  <si>
+    <t>135541132</t>
+  </si>
+  <si>
+    <t>135546387</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 05.12.2025</t>
   </si>
 </sst>
 </file>
@@ -541,16 +547,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135500230</v>
+        <v>135633437</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -558,16 +564,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135487116</v>
+        <v>135728262</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -575,16 +581,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -592,16 +598,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -609,16 +615,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -626,16 +632,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -659,31 +665,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0878536E-84AA-4AE8-87C4-2BF2D8D0B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8802637-6E5B-45D0-A5F8-0D3C8000C4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1230" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusa Sicoob 06.12.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 06.12.2025</t>
-  </si>
-  <si>
-    <t>135547919</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 05.12.2025</t>
-  </si>
-  <si>
-    <t>135677574</t>
-  </si>
-  <si>
-    <t>135541132</t>
-  </si>
-  <si>
-    <t>135546387</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 05.12.2025</t>
+    <t>Relatório de Recusa SICOOB 08.12.2025</t>
+  </si>
+  <si>
+    <t>135614170</t>
+  </si>
+  <si>
+    <t>135656489</t>
+  </si>
+  <si>
+    <t>134555722</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -515,7 +506,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -547,16 +538,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135633437</v>
+        <v>135638617</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -564,16 +555,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135728262</v>
+        <v>135600181</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -581,16 +572,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -598,16 +589,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -615,35 +606,18 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -665,31 +639,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC192C1D-FAE7-413A-9301-E0F0C3302117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB08ED47-249D-40BC-96D7-32BA19FA7B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>134875044</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 24.10.2025</t>
-  </si>
-  <si>
-    <t>135074734</t>
-  </si>
-  <si>
-    <t>134980797</t>
-  </si>
-  <si>
-    <t>134968908</t>
-  </si>
-  <si>
-    <t>134974393</t>
-  </si>
-  <si>
-    <t>133425615</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.10.2025</t>
+    <t>131891065</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 19.12.2025</t>
+  </si>
+  <si>
+    <t>135841892</t>
+  </si>
+  <si>
+    <t>135865381</t>
+  </si>
+  <si>
+    <t>135946066</t>
+  </si>
+  <si>
+    <t>132266796</t>
+  </si>
+  <si>
+    <t>135777720</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 19.12.2025</t>
+  </si>
+  <si>
+    <t>135728550</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 20.12.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 20.12.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -603,6 +612,23 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB08ED47-249D-40BC-96D7-32BA19FA7B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178C40E-36BD-40FD-904A-2C653276FA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,49 @@
     <t>971</t>
   </si>
   <si>
-    <t>131891065</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 19.12.2025</t>
-  </si>
-  <si>
-    <t>135841892</t>
-  </si>
-  <si>
-    <t>135865381</t>
-  </si>
-  <si>
-    <t>135946066</t>
-  </si>
-  <si>
-    <t>132266796</t>
-  </si>
-  <si>
-    <t>135777720</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 19.12.2025</t>
-  </si>
-  <si>
-    <t>135728550</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 20.12.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 20.12.2025</t>
+    <t>135789324</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 22.12.2025</t>
+  </si>
+  <si>
+    <t>135788545</t>
+  </si>
+  <si>
+    <t>135921661</t>
+  </si>
+  <si>
+    <t>135790924</t>
+  </si>
+  <si>
+    <t>135923398</t>
+  </si>
+  <si>
+    <t>135941893</t>
+  </si>
+  <si>
+    <t>135957111</t>
+  </si>
+  <si>
+    <t>135970852</t>
+  </si>
+  <si>
+    <t>135974616</t>
+  </si>
+  <si>
+    <t>135974850</t>
+  </si>
+  <si>
+    <t>131700181</t>
+  </si>
+  <si>
+    <t>135865566</t>
+  </si>
+  <si>
+    <t>135983440</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 22.12.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +492,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +550,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +567,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -606,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -614,18 +626,120 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -643,31 +757,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178C40E-36BD-40FD-904A-2C653276FA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5F9433-D810-4272-87D2-E18D5C08F8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,58 @@
     <t>971</t>
   </si>
   <si>
-    <t>135789324</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 22.12.2025</t>
-  </si>
-  <si>
-    <t>135788545</t>
-  </si>
-  <si>
-    <t>135921661</t>
-  </si>
-  <si>
-    <t>135790924</t>
-  </si>
-  <si>
-    <t>135923398</t>
-  </si>
-  <si>
-    <t>135941893</t>
-  </si>
-  <si>
-    <t>135957111</t>
-  </si>
-  <si>
-    <t>135970852</t>
-  </si>
-  <si>
-    <t>135974616</t>
-  </si>
-  <si>
-    <t>135974850</t>
-  </si>
-  <si>
-    <t>131700181</t>
-  </si>
-  <si>
-    <t>135865566</t>
-  </si>
-  <si>
-    <t>135983440</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 22.12.2025</t>
+    <t>135837745</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 23.12.2025</t>
+  </si>
+  <si>
+    <t>135882942</t>
+  </si>
+  <si>
+    <t>135806237</t>
+  </si>
+  <si>
+    <t>135886658</t>
+  </si>
+  <si>
+    <t>135935629</t>
+  </si>
+  <si>
+    <t>135985348</t>
+  </si>
+  <si>
+    <t>135814338</t>
+  </si>
+  <si>
+    <t>135818983</t>
+  </si>
+  <si>
+    <t>135828052</t>
+  </si>
+  <si>
+    <t>135845084</t>
+  </si>
+  <si>
+    <t>132420030</t>
+  </si>
+  <si>
+    <t>135837987</t>
+  </si>
+  <si>
+    <t>135996699</t>
+  </si>
+  <si>
+    <t>135886826</t>
+  </si>
+  <si>
+    <t>135816323</t>
+  </si>
+  <si>
+    <t>135859268</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 23.12.2025</t>
   </si>
 </sst>
 </file>
@@ -492,7 +501,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -533,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -550,7 +559,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -567,7 +576,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -584,7 +593,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -601,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -618,7 +627,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -635,7 +644,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -652,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -669,7 +678,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -686,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -703,7 +712,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -720,7 +729,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -737,9 +746,60 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -757,31 +817,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5F9433-D810-4272-87D2-E18D5C08F8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021F302C-214C-44B4-A3BC-C4C14BF6B335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>135837745</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 23.12.2025</t>
-  </si>
-  <si>
-    <t>135882942</t>
-  </si>
-  <si>
-    <t>135806237</t>
-  </si>
-  <si>
-    <t>135886658</t>
-  </si>
-  <si>
-    <t>135935629</t>
-  </si>
-  <si>
-    <t>135985348</t>
-  </si>
-  <si>
-    <t>135814338</t>
-  </si>
-  <si>
-    <t>135818983</t>
-  </si>
-  <si>
-    <t>135828052</t>
-  </si>
-  <si>
-    <t>135845084</t>
-  </si>
-  <si>
-    <t>132420030</t>
-  </si>
-  <si>
-    <t>135837987</t>
-  </si>
-  <si>
-    <t>135996699</t>
-  </si>
-  <si>
-    <t>135886826</t>
-  </si>
-  <si>
-    <t>135816323</t>
-  </si>
-  <si>
-    <t>135859268</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 23.12.2025</t>
+    <t>135880958</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 24.12.2025</t>
+  </si>
+  <si>
+    <t>135896299</t>
+  </si>
+  <si>
+    <t>135896547</t>
+  </si>
+  <si>
+    <t>135925047</t>
+  </si>
+  <si>
+    <t>135816267</t>
+  </si>
+  <si>
+    <t>136014954</t>
+  </si>
+  <si>
+    <t>135863910</t>
+  </si>
+  <si>
+    <t>135908373</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 24.12.2025</t>
   </si>
 </sst>
 </file>
@@ -501,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -542,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -559,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -576,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -593,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -610,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -627,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -644,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -661,145 +637,9 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -817,31 +657,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021F302C-214C-44B4-A3BC-C4C14BF6B335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBF2380-B823-4A95-98DA-FDC070E488E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,88 @@
     <t>971</t>
   </si>
   <si>
-    <t>135880958</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 24.12.2025</t>
-  </si>
-  <si>
-    <t>135896299</t>
-  </si>
-  <si>
-    <t>135896547</t>
-  </si>
-  <si>
-    <t>135925047</t>
-  </si>
-  <si>
-    <t>135816267</t>
-  </si>
-  <si>
-    <t>136014954</t>
-  </si>
-  <si>
-    <t>135863910</t>
-  </si>
-  <si>
-    <t>135908373</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.12.2025</t>
+    <t>135893201</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 26.12.2025</t>
+  </si>
+  <si>
+    <t>135891219</t>
+  </si>
+  <si>
+    <t>135891020</t>
+  </si>
+  <si>
+    <t>135889246</t>
+  </si>
+  <si>
+    <t>135944402</t>
+  </si>
+  <si>
+    <t>135959602</t>
+  </si>
+  <si>
+    <t>135948500</t>
+  </si>
+  <si>
+    <t>135941104</t>
+  </si>
+  <si>
+    <t>135984986</t>
+  </si>
+  <si>
+    <t>135919088</t>
+  </si>
+  <si>
+    <t>135885086</t>
+  </si>
+  <si>
+    <t>136014521</t>
+  </si>
+  <si>
+    <t>135850545</t>
+  </si>
+  <si>
+    <t>135852815</t>
+  </si>
+  <si>
+    <t>136027861</t>
+  </si>
+  <si>
+    <t>135885486</t>
+  </si>
+  <si>
+    <t>135886094</t>
+  </si>
+  <si>
+    <t>135888864</t>
+  </si>
+  <si>
+    <t>135837503</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 26.12.2025</t>
+  </si>
+  <si>
+    <t>135886351</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 27.12.2025</t>
+  </si>
+  <si>
+    <t>135875540</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 27.12.2025</t>
+  </si>
+  <si>
+    <t>134831307</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 28.12.2025</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 28.12.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -603,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -620,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -637,9 +691,247 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBF2380-B823-4A95-98DA-FDC070E488E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD09C2B-1D46-44D1-BC50-CEF94EA0C886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>135893201</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 26.12.2025</t>
-  </si>
-  <si>
-    <t>135891219</t>
-  </si>
-  <si>
-    <t>135891020</t>
-  </si>
-  <si>
-    <t>135889246</t>
-  </si>
-  <si>
-    <t>135944402</t>
-  </si>
-  <si>
-    <t>135959602</t>
-  </si>
-  <si>
-    <t>135948500</t>
-  </si>
-  <si>
-    <t>135941104</t>
-  </si>
-  <si>
-    <t>135984986</t>
-  </si>
-  <si>
-    <t>135919088</t>
-  </si>
-  <si>
-    <t>135885086</t>
-  </si>
-  <si>
-    <t>136014521</t>
-  </si>
-  <si>
-    <t>135850545</t>
-  </si>
-  <si>
-    <t>135852815</t>
-  </si>
-  <si>
-    <t>136027861</t>
-  </si>
-  <si>
-    <t>135885486</t>
-  </si>
-  <si>
-    <t>135886094</t>
-  </si>
-  <si>
-    <t>135888864</t>
-  </si>
-  <si>
-    <t>135837503</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 26.12.2025</t>
-  </si>
-  <si>
-    <t>135886351</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 27.12.2025</t>
-  </si>
-  <si>
-    <t>135875540</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 27.12.2025</t>
-  </si>
-  <si>
-    <t>134831307</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 28.12.2025</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 28.12.2025</t>
+    <t>135870175</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 29.12.2025</t>
+  </si>
+  <si>
+    <t>135973845</t>
+  </si>
+  <si>
+    <t>135927559</t>
+  </si>
+  <si>
+    <t>135993330</t>
+  </si>
+  <si>
+    <t>135786816</t>
+  </si>
+  <si>
+    <t>135949618</t>
+  </si>
+  <si>
+    <t>135963090</t>
+  </si>
+  <si>
+    <t>135909717</t>
+  </si>
+  <si>
+    <t>135925955</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 29.12.2025</t>
   </si>
 </sst>
 </file>
@@ -531,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -606,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -640,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -657,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -674,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -708,230 +657,9 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -949,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD09C2B-1D46-44D1-BC50-CEF94EA0C886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9855D98-C26A-4739-82C8-204AD4FD94A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>135870175</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 29.12.2025</t>
-  </si>
-  <si>
-    <t>135973845</t>
-  </si>
-  <si>
-    <t>135927559</t>
-  </si>
-  <si>
-    <t>135993330</t>
-  </si>
-  <si>
-    <t>135786816</t>
-  </si>
-  <si>
-    <t>135949618</t>
-  </si>
-  <si>
-    <t>135963090</t>
-  </si>
-  <si>
-    <t>135909717</t>
-  </si>
-  <si>
-    <t>135925955</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 29.12.2025</t>
+    <t>136037044</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 30.12.25</t>
+  </si>
+  <si>
+    <t>136050526</t>
+  </si>
+  <si>
+    <t>135837503</t>
+  </si>
+  <si>
+    <t>135990509</t>
+  </si>
+  <si>
+    <t>135985125</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 30.12.25</t>
+  </si>
+  <si>
+    <t>135949344</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 01.01.26</t>
+  </si>
+  <si>
+    <t>135922904</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 01.01.2026</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -614,52 +614,18 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -677,31 +643,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9855D98-C26A-4739-82C8-204AD4FD94A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8329DA-919C-4FED-A0AF-D25961351F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,64 @@
     <t>971</t>
   </si>
   <si>
-    <t>136037044</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 30.12.25</t>
-  </si>
-  <si>
-    <t>136050526</t>
-  </si>
-  <si>
-    <t>135837503</t>
-  </si>
-  <si>
-    <t>135990509</t>
-  </si>
-  <si>
-    <t>135985125</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 30.12.25</t>
-  </si>
-  <si>
-    <t>135949344</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 01.01.26</t>
-  </si>
-  <si>
     <t>135922904</t>
   </si>
   <si>
-    <t>Recusa Sicoob 01.01.2026</t>
+    <t>136007316</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 02.01.2026</t>
+  </si>
+  <si>
+    <t>136053503</t>
+  </si>
+  <si>
+    <t>136049822</t>
+  </si>
+  <si>
+    <t>136034118</t>
+  </si>
+  <si>
+    <t>134933551</t>
+  </si>
+  <si>
+    <t>135979393</t>
+  </si>
+  <si>
+    <t>135978938</t>
+  </si>
+  <si>
+    <t>135999400</t>
+  </si>
+  <si>
+    <t>135992519</t>
+  </si>
+  <si>
+    <t>136021110</t>
+  </si>
+  <si>
+    <t>136087886</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 02.01.2026</t>
+  </si>
+  <si>
+    <t>136052548</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 03.01.2026</t>
+  </si>
+  <si>
+    <t>135983075</t>
+  </si>
+  <si>
+    <t>135991993</t>
+  </si>
+  <si>
+    <t>135985475</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 03.01.2026</t>
   </si>
 </sst>
 </file>
@@ -480,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,16 +539,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,16 +556,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -546,16 +573,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -563,16 +590,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -580,16 +607,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -597,16 +624,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -614,18 +641,171 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8329DA-919C-4FED-A0AF-D25961351F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C05B24-6D58-4102-9F9B-4B006D95B53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,64 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>135922904</t>
-  </si>
-  <si>
-    <t>136007316</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 02.01.2026</t>
-  </si>
-  <si>
-    <t>136053503</t>
-  </si>
-  <si>
-    <t>136049822</t>
-  </si>
-  <si>
-    <t>136034118</t>
-  </si>
-  <si>
-    <t>134933551</t>
-  </si>
-  <si>
-    <t>135979393</t>
-  </si>
-  <si>
-    <t>135978938</t>
-  </si>
-  <si>
-    <t>135999400</t>
-  </si>
-  <si>
-    <t>135992519</t>
-  </si>
-  <si>
-    <t>136021110</t>
-  </si>
-  <si>
-    <t>136087886</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 02.01.2026</t>
-  </si>
-  <si>
-    <t>136052548</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 03.01.2026</t>
-  </si>
-  <si>
-    <t>135983075</t>
-  </si>
-  <si>
-    <t>135991993</t>
-  </si>
-  <si>
-    <t>135985475</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 03.01.2026</t>
+    <t>136056481</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 05.01.2026</t>
+  </si>
+  <si>
+    <t>136079052</t>
+  </si>
+  <si>
+    <t>135581914</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 05.01.2026</t>
   </si>
 </sst>
 </file>
@@ -539,16 +494,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -556,16 +511,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -573,241 +528,32 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -823,31 +569,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C05B24-6D58-4102-9F9B-4B006D95B53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D66D1D-1F7C-4289-A35A-BDA8036DB4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>136056481</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 05.01.2026</t>
-  </si>
-  <si>
-    <t>136079052</t>
-  </si>
-  <si>
-    <t>135581914</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 05.01.2026</t>
+    <t>136022436</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 06.01.2026</t>
+  </si>
+  <si>
+    <t>136080850</t>
+  </si>
+  <si>
+    <t>136016302</t>
+  </si>
+  <si>
+    <t>134868244</t>
+  </si>
+  <si>
+    <t>136102133</t>
+  </si>
+  <si>
+    <t>135452487</t>
+  </si>
+  <si>
+    <t>136027602</t>
+  </si>
+  <si>
+    <t>136059336</t>
+  </si>
+  <si>
+    <t>136087110</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 06.01.2026</t>
   </si>
 </sst>
 </file>
@@ -503,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -520,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -537,9 +555,111 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -569,31 +689,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D66D1D-1F7C-4289-A35A-BDA8036DB4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DD4D25-B9F1-4983-A2DB-08994B8D05BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>136022436</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 06.01.2026</t>
-  </si>
-  <si>
-    <t>136080850</t>
-  </si>
-  <si>
-    <t>136016302</t>
-  </si>
-  <si>
-    <t>134868244</t>
-  </si>
-  <si>
-    <t>136102133</t>
-  </si>
-  <si>
-    <t>135452487</t>
-  </si>
-  <si>
-    <t>136027602</t>
-  </si>
-  <si>
-    <t>136059336</t>
-  </si>
-  <si>
-    <t>136087110</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 06.01.2026</t>
+    <t>136066486</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 07.01.2026</t>
+  </si>
+  <si>
+    <t>136085473</t>
+  </si>
+  <si>
+    <t>136084111</t>
+  </si>
+  <si>
+    <t>136109677</t>
+  </si>
+  <si>
+    <t>135957165</t>
+  </si>
+  <si>
+    <t>133455635</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 07.01.2026</t>
   </si>
 </sst>
 </file>
@@ -521,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,7 +580,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -606,60 +597,9 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -689,31 +629,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DD4D25-B9F1-4983-A2DB-08994B8D05BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1C6446-FE56-414B-A446-E2F78212A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>136066486</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 07.01.2026</t>
-  </si>
-  <si>
-    <t>136085473</t>
-  </si>
-  <si>
-    <t>136084111</t>
-  </si>
-  <si>
-    <t>136109677</t>
-  </si>
-  <si>
-    <t>135957165</t>
-  </si>
-  <si>
-    <t>133455635</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 07.01.2026</t>
+    <t>136031136</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 08.01.2026</t>
+  </si>
+  <si>
+    <t>136077790</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 08.01.2026</t>
   </si>
 </sst>
 </file>
@@ -512,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,77 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -629,31 +549,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1C6446-FE56-414B-A446-E2F78212A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5889D13-C7BE-4FA4-A480-909189500C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,58 @@
     <t>971</t>
   </si>
   <si>
-    <t>136031136</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 08.01.2026</t>
-  </si>
-  <si>
-    <t>136077790</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 08.01.2026</t>
+    <t>136063890</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 10.01.2026</t>
+  </si>
+  <si>
+    <t>136163389</t>
+  </si>
+  <si>
+    <t>136039774</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 10.01.2026</t>
+  </si>
+  <si>
+    <t>136079764</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 09.01.2026</t>
+  </si>
+  <si>
+    <t>136139999</t>
+  </si>
+  <si>
+    <t>136166477</t>
+  </si>
+  <si>
+    <t>132420030</t>
+  </si>
+  <si>
+    <t>136045665</t>
+  </si>
+  <si>
+    <t>136049880</t>
+  </si>
+  <si>
+    <t>136040768</t>
+  </si>
+  <si>
+    <t>136178520</t>
+  </si>
+  <si>
+    <t>136066664</t>
+  </si>
+  <si>
+    <t>136070638</t>
+  </si>
+  <si>
+    <t>136046500</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 09.01.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +501,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,23 +559,215 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5889D13-C7BE-4FA4-A480-909189500C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C503A3-7C2F-4A04-9FFF-03495B6C9AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,58 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>136063890</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 10.01.2026</t>
-  </si>
-  <si>
-    <t>136163389</t>
-  </si>
-  <si>
-    <t>136039774</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 10.01.2026</t>
-  </si>
-  <si>
-    <t>136079764</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 09.01.2026</t>
-  </si>
-  <si>
-    <t>136139999</t>
-  </si>
-  <si>
-    <t>136166477</t>
-  </si>
-  <si>
-    <t>132420030</t>
-  </si>
-  <si>
-    <t>136045665</t>
-  </si>
-  <si>
-    <t>136049880</t>
-  </si>
-  <si>
-    <t>136040768</t>
-  </si>
-  <si>
-    <t>136178520</t>
-  </si>
-  <si>
-    <t>136066664</t>
-  </si>
-  <si>
-    <t>136070638</t>
-  </si>
-  <si>
-    <t>136046500</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 09.01.2026</t>
+    <t>136143140</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 12.01.2026</t>
+  </si>
+  <si>
+    <t>136154436</t>
+  </si>
+  <si>
+    <t>136104488</t>
+  </si>
+  <si>
+    <t>136065318</t>
+  </si>
+  <si>
+    <t>136202251</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 12.01.2026</t>
   </si>
 </sst>
 </file>
@@ -542,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -559,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -576,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -584,16 +551,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -601,173 +568,41 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D7" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -783,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C503A3-7C2F-4A04-9FFF-03495B6C9AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A7A4EF-18FF-4705-A23A-0E6FC67A8951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>136143140</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 12.01.2026</t>
-  </si>
-  <si>
-    <t>136154436</t>
-  </si>
-  <si>
-    <t>136104488</t>
-  </si>
-  <si>
-    <t>136065318</t>
-  </si>
-  <si>
-    <t>136202251</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 12.01.2026</t>
+    <t>136076755</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 13.01.2026</t>
+  </si>
+  <si>
+    <t>136086363</t>
+  </si>
+  <si>
+    <t>136077987</t>
+  </si>
+  <si>
+    <t>136106757</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 13.01.2026</t>
   </si>
 </sst>
 </file>
@@ -509,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,7 +540,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,28 +557,14 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D7" s="1"/>
@@ -618,31 +601,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A7A4EF-18FF-4705-A23A-0E6FC67A8951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C35B51-EC8F-457D-B45C-1C07C5922C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>136076755</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 13.01.2026</t>
-  </si>
-  <si>
-    <t>136086363</t>
-  </si>
-  <si>
-    <t>136077987</t>
-  </si>
-  <si>
-    <t>136106757</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 13.01.2026</t>
+    <t>136124049</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 14.01.2026</t>
+  </si>
+  <si>
+    <t>136142489</t>
+  </si>
+  <si>
+    <t>136216147</t>
+  </si>
+  <si>
+    <t>136122579</t>
+  </si>
+  <si>
+    <t>136159329</t>
+  </si>
+  <si>
+    <t>136218358</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -506,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,17 +563,45 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D9" s="1"/>
@@ -601,31 +635,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C35B51-EC8F-457D-B45C-1C07C5922C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459EDFE2-07B7-405C-BED4-7F62E4434433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,33 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>136124049</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 14.01.2026</t>
-  </si>
-  <si>
-    <t>136142489</t>
-  </si>
-  <si>
-    <t>136216147</t>
-  </si>
-  <si>
-    <t>136122579</t>
-  </si>
-  <si>
-    <t>136159329</t>
-  </si>
-  <si>
-    <t>136218358</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -471,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -502,124 +475,84 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -635,31 +568,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459EDFE2-07B7-405C-BED4-7F62E4434433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,30 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136215818</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 15.01.2026</t>
+  </si>
+  <si>
+    <t>136216009</t>
+  </si>
+  <si>
+    <t>136085695</t>
+  </si>
+  <si>
+    <t>131804542</t>
+  </si>
+  <si>
+    <t>136267791</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 15.01.2025</t>
   </si>
 </sst>
 </file>
@@ -444,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,82 +499,87 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -568,31 +597,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387C15F6-6B5E-4DB8-8EE5-B0AEECFCB470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,43 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136215818</t>
+    <t>136181957</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 15.01.2026</t>
-  </si>
-  <si>
-    <t>136216009</t>
-  </si>
-  <si>
-    <t>136085695</t>
-  </si>
-  <si>
-    <t>131804542</t>
-  </si>
-  <si>
-    <t>136267791</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 15.01.2025</t>
+    <t>Relatório de Recusa SICOOB 16.01.2026</t>
+  </si>
+  <si>
+    <t>136246027</t>
+  </si>
+  <si>
+    <t>136256273</t>
+  </si>
+  <si>
+    <t>136186277</t>
+  </si>
+  <si>
+    <t>136111393</t>
+  </si>
+  <si>
+    <t>136126785</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 16.01.2025</t>
+  </si>
+  <si>
+    <t>136242353</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 17.01.2026</t>
+  </si>
+  <si>
+    <t>136114785</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 17.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +541,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,7 +558,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,7 +575,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,9 +592,60 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -597,31 +663,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387C15F6-6B5E-4DB8-8EE5-B0AEECFCB470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8FEEA2-323A-45A0-A6F8-B082910554BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,43 +51,40 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136181957</t>
+    <t>136165481</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 16.01.2026</t>
-  </si>
-  <si>
-    <t>136246027</t>
-  </si>
-  <si>
-    <t>136256273</t>
-  </si>
-  <si>
-    <t>136186277</t>
-  </si>
-  <si>
-    <t>136111393</t>
-  </si>
-  <si>
-    <t>136126785</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 16.01.2025</t>
-  </si>
-  <si>
-    <t>136242353</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 17.01.2026</t>
-  </si>
-  <si>
-    <t>136114785</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 17.01.2026</t>
+    <t>Relatório de Recusa SICOOB 19.01.2026</t>
+  </si>
+  <si>
+    <t>136221950</t>
+  </si>
+  <si>
+    <t>136251926</t>
+  </si>
+  <si>
+    <t>136270596</t>
+  </si>
+  <si>
+    <t>136271594</t>
+  </si>
+  <si>
+    <t>136214407</t>
+  </si>
+  <si>
+    <t>136283106</t>
+  </si>
+  <si>
+    <t>136286147</t>
+  </si>
+  <si>
+    <t>136308801</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 19.01.2026</t>
   </si>
 </sst>
 </file>
@@ -483,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -524,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -541,7 +538,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -558,7 +555,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -575,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -592,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -609,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -617,16 +614,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -634,18 +631,35 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -663,31 +677,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8FEEA2-323A-45A0-A6F8-B082910554BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8DA109-69DC-439C-A4F5-8CA94C283FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,40 +51,28 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136165481</t>
+    <t>122466646</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 19.01.2026</t>
-  </si>
-  <si>
-    <t>136221950</t>
-  </si>
-  <si>
-    <t>136251926</t>
-  </si>
-  <si>
-    <t>136270596</t>
-  </si>
-  <si>
-    <t>136271594</t>
-  </si>
-  <si>
-    <t>136214407</t>
-  </si>
-  <si>
-    <t>136283106</t>
-  </si>
-  <si>
-    <t>136286147</t>
-  </si>
-  <si>
-    <t>136308801</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 19.01.2026</t>
+    <t>Relatório de Recusa SICOOB 20.01.2026</t>
+  </si>
+  <si>
+    <t>122466927</t>
+  </si>
+  <si>
+    <t>136271797</t>
+  </si>
+  <si>
+    <t>131712233</t>
+  </si>
+  <si>
+    <t>136335825</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 20.01.2026</t>
   </si>
 </sst>
 </file>
@@ -480,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,7 +543,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,77 +577,9 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8DA109-69DC-439C-A4F5-8CA94C283FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A36FD1-693D-4B58-9E96-B4390BD51D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,19 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>122466646</t>
+    <t>136151437</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 20.01.2026</t>
-  </si>
-  <si>
-    <t>122466927</t>
-  </si>
-  <si>
-    <t>136271797</t>
-  </si>
-  <si>
-    <t>131712233</t>
-  </si>
-  <si>
-    <t>136335825</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 20.01.2026</t>
+    <t>Relatório de Recusa SICOOB 21.01.2026</t>
+  </si>
+  <si>
+    <t>136210760</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 21.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,60 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A36FD1-693D-4B58-9E96-B4390BD51D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3841E447-7107-424E-8806-E9D14CC6C865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,19 +51,28 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136151437</t>
+    <t>136280325</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 21.01.2026</t>
-  </si>
-  <si>
-    <t>136210760</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 21.01.2026</t>
+    <t>Relatório de Recusa SICOOB 22.01.2026</t>
+  </si>
+  <si>
+    <t>136354506</t>
+  </si>
+  <si>
+    <t>136135482</t>
+  </si>
+  <si>
+    <t>136363513</t>
+  </si>
+  <si>
+    <t>136270604</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 22.01.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,9 +526,60 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3841E447-7107-424E-8806-E9D14CC6C865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6A7CFE-9634-4F32-B212-AC958C589C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,40 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136280325</t>
+    <t>136200480</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 22.01.2026</t>
-  </si>
-  <si>
-    <t>136354506</t>
-  </si>
-  <si>
-    <t>136135482</t>
-  </si>
-  <si>
-    <t>136363513</t>
-  </si>
-  <si>
-    <t>136270604</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 22.01.2026</t>
+    <t>Relatório de Recusa SICOOB 24.01.2026</t>
+  </si>
+  <si>
+    <t>136247997</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 24.01.2026</t>
+  </si>
+  <si>
+    <t>136328217</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 23.01.2026</t>
+  </si>
+  <si>
+    <t>136366949</t>
+  </si>
+  <si>
+    <t>133090534</t>
+  </si>
+  <si>
+    <t>136390733</t>
+  </si>
+  <si>
+    <t>136262946</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -508,8 +520,8 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -525,25 +537,25 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -551,16 +563,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -568,18 +580,52 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -597,31 +643,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6A7CFE-9634-4F32-B212-AC958C589C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,42 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136200480</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 24.01.2026</t>
-  </si>
-  <si>
-    <t>136247997</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.01.2026</t>
-  </si>
-  <si>
-    <t>136328217</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 23.01.2026</t>
-  </si>
-  <si>
-    <t>136366949</t>
-  </si>
-  <si>
-    <t>133090534</t>
-  </si>
-  <si>
-    <t>136390733</t>
-  </si>
-  <si>
-    <t>136262946</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -480,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -511,121 +475,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA46AF21-B62C-488D-8118-60F012D432B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,24 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136239519</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 26.01.2026</t>
+  </si>
+  <si>
+    <t>136288006</t>
+  </si>
+  <si>
+    <t>134332639</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +493,53 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +557,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA46AF21-B62C-488D-8118-60F012D432B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,24 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136239519</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 26.01.2026</t>
-  </si>
-  <si>
-    <t>136288006</t>
-  </si>
-  <si>
-    <t>134332639</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -493,53 +475,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +513,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0D450C-5D36-4BF2-B623-3744978C87A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,30 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136273112</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 27.01.2026</t>
+  </si>
+  <si>
+    <t>136346989</t>
+  </si>
+  <si>
+    <t>136402499</t>
+  </si>
+  <si>
+    <t>136269877</t>
+  </si>
+  <si>
+    <t>136289559</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 27.01.2026</t>
   </si>
 </sst>
 </file>
@@ -475,26 +499,86 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
@@ -513,31 +597,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0D450C-5D36-4BF2-B623-3744978C87A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE694871-284C-4CC3-BF62-7FFEF5DB84C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136273112</t>
+    <t>136387637</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 27.01.2026</t>
-  </si>
-  <si>
-    <t>136346989</t>
-  </si>
-  <si>
-    <t>136402499</t>
-  </si>
-  <si>
-    <t>136269877</t>
-  </si>
-  <si>
-    <t>136289559</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 27.01.2026</t>
+    <t>Relatório de Recusa SICOOB 28.01.2026</t>
+  </si>
+  <si>
+    <t>136394146</t>
+  </si>
+  <si>
+    <t>136451653</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,43 +537,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE694871-284C-4CC3-BF62-7FFEF5DB84C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,24 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136387637</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 28.01.2026</t>
-  </si>
-  <si>
-    <t>136394146</t>
-  </si>
-  <si>
-    <t>136451653</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -493,53 +475,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +513,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA71F3CA-CA58-4687-ADED-5886F0A8AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,30 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136449317</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 29.01.2026</t>
+  </si>
+  <si>
+    <t>136331331</t>
+  </si>
+  <si>
+    <t>136386459</t>
+  </si>
+  <si>
+    <t>136312914</t>
+  </si>
+  <si>
+    <t>136316045</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -475,26 +499,86 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
@@ -513,31 +597,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA71F3CA-CA58-4687-ADED-5886F0A8AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F0D0A0-8DF2-42FA-9F9F-5A37DFD3045F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,37 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136449317</t>
+    <t>136321923</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 29.01.2026</t>
-  </si>
-  <si>
-    <t>136331331</t>
-  </si>
-  <si>
-    <t>136386459</t>
-  </si>
-  <si>
-    <t>136312914</t>
-  </si>
-  <si>
-    <t>136316045</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 29.01.2026</t>
+    <t>Relatório de Recusa SICOOB 30.01.2026</t>
+  </si>
+  <si>
+    <t>136405937</t>
+  </si>
+  <si>
+    <t>136462966</t>
+  </si>
+  <si>
+    <t>136326449</t>
+  </si>
+  <si>
+    <t>135858984</t>
+  </si>
+  <si>
+    <t>136415668</t>
+  </si>
+  <si>
+    <t>136322443</t>
+  </si>
+  <si>
+    <t>136330218</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 30.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,7 +552,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -560,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -577,9 +586,60 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F0D0A0-8DF2-42FA-9F9F-5A37DFD3045F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005D9BA5-4365-44B3-8D65-991FBD6FFFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,37 +51,34 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136321923</t>
+    <t>134332639</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 30.01.2026</t>
-  </si>
-  <si>
-    <t>136405937</t>
-  </si>
-  <si>
-    <t>136462966</t>
-  </si>
-  <si>
-    <t>136326449</t>
-  </si>
-  <si>
-    <t>135858984</t>
-  </si>
-  <si>
-    <t>136415668</t>
-  </si>
-  <si>
-    <t>136322443</t>
-  </si>
-  <si>
-    <t>136330218</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 30.01.2026</t>
+    <t>Relatório de Recusa SICOOB 02.02.2026</t>
+  </si>
+  <si>
+    <t>136374739</t>
+  </si>
+  <si>
+    <t>136403440</t>
+  </si>
+  <si>
+    <t>136422896</t>
+  </si>
+  <si>
+    <t>136503030</t>
+  </si>
+  <si>
+    <t>136405816</t>
+  </si>
+  <si>
+    <t>136415139</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 02.02.2026</t>
   </si>
 </sst>
 </file>
@@ -477,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -535,7 +532,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -552,7 +549,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -569,7 +566,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -586,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -603,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -620,26 +617,9 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005D9BA5-4365-44B3-8D65-991FBD6FFFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9488DFF2-ABE3-40F2-BFDF-FE6CFD2A943A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,34 +51,25 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>134332639</t>
+    <t>136384079</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 02.02.2026</t>
-  </si>
-  <si>
-    <t>136374739</t>
-  </si>
-  <si>
-    <t>136403440</t>
-  </si>
-  <si>
-    <t>136422896</t>
-  </si>
-  <si>
-    <t>136503030</t>
-  </si>
-  <si>
-    <t>136405816</t>
-  </si>
-  <si>
-    <t>136415139</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 02.02.2026</t>
+    <t>Relatório de Recusa SICOOB 03.02.2026</t>
+  </si>
+  <si>
+    <t>136441536</t>
+  </si>
+  <si>
+    <t>136516325</t>
+  </si>
+  <si>
+    <t>132695631</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 03.02.2026</t>
   </si>
 </sst>
 </file>
@@ -474,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -532,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -549,7 +540,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -566,60 +557,9 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9488DFF2-ABE3-40F2-BFDF-FE6CFD2A943A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473C9ED-2A5C-4579-BC28-3AD4AF9DC3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,25 +51,25 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136384079</t>
+    <t>136400633</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 03.02.2026</t>
-  </si>
-  <si>
-    <t>136441536</t>
-  </si>
-  <si>
-    <t>136516325</t>
-  </si>
-  <si>
-    <t>132695631</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 03.02.2026</t>
+    <t>Relatório de Recusa SICOOB 04.02.2026</t>
+  </si>
+  <si>
+    <t>136471778</t>
+  </si>
+  <si>
+    <t>136453104</t>
+  </si>
+  <si>
+    <t>136386069</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 04.02.2026</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473C9ED-2A5C-4579-BC28-3AD4AF9DC3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,27 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136400633</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 04.02.2026</t>
-  </si>
-  <si>
-    <t>136471778</t>
-  </si>
-  <si>
-    <t>136453104</t>
-  </si>
-  <si>
-    <t>136386069</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 04.02.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -496,70 +475,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -577,31 +513,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9915D2-AE4C-4C1F-BBC6-79243482DF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136556004</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 05.02.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 05.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +487,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +517,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9915D2-AE4C-4C1F-BBC6-79243482DF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60431124-2B1D-4B70-BFDD-6F49B8F2805F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,16 +51,37 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136556004</t>
+    <t>136431417</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 05.02.2026</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 05.02.2026</t>
+    <t>Relatório de Recusa SICOOB 08.02.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 08.02.2026</t>
+  </si>
+  <si>
+    <t>136532027</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 06.02,2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 06.02.2026</t>
+  </si>
+  <si>
+    <t>136572241</t>
+  </si>
+  <si>
+    <t>136578772</t>
+  </si>
+  <si>
+    <t>136434109</t>
+  </si>
+  <si>
+    <t>136596239</t>
   </si>
 </sst>
 </file>
@@ -456,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,6 +524,91 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60431124-2B1D-4B70-BFDD-6F49B8F2805F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,39 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136431417</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 08.02.2026</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 08.02.2026</t>
-  </si>
-  <si>
-    <t>136532027</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa SICOOB 06.02,2026</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 06.02.2026</t>
-  </si>
-  <si>
-    <t>136572241</t>
-  </si>
-  <si>
-    <t>136578772</t>
-  </si>
-  <si>
-    <t>136434109</t>
-  </si>
-  <si>
-    <t>136596239</t>
   </si>
 </sst>
 </file>
@@ -477,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -508,104 +475,27 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -623,31 +513,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BA57B0-3633-4D1E-847C-9F745FA1219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136480512</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 09.02.2026</t>
+  </si>
+  <si>
+    <t>136557168</t>
+  </si>
+  <si>
+    <t>136537128</t>
+  </si>
+  <si>
+    <t>136648842</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +496,70 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +577,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BA57B0-3633-4D1E-847C-9F745FA1219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D76FF40-9FE4-4478-A235-C7C93E972533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,25 +51,31 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136480512</t>
+    <t>136476721</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 09.02.2026</t>
-  </si>
-  <si>
-    <t>136557168</t>
-  </si>
-  <si>
-    <t>136537128</t>
-  </si>
-  <si>
-    <t>136648842</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 09.02.2026</t>
+    <t>Relatório de Recusa SICOOB 10.02.2026</t>
+  </si>
+  <si>
+    <t>136573318</t>
+  </si>
+  <si>
+    <t>136438793</t>
+  </si>
+  <si>
+    <t>136434239</t>
+  </si>
+  <si>
+    <t>136680957</t>
+  </si>
+  <si>
+    <t>133890056</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 10.02.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -523,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -540,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -557,9 +563,43 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D76FF40-9FE4-4478-A235-C7C93E972533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97864DC9-909D-4AA4-A9E7-D821A4F235AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,31 +51,19 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136476721</t>
+    <t>132441027</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 10.02.2026</t>
-  </si>
-  <si>
-    <t>136573318</t>
-  </si>
-  <si>
-    <t>136438793</t>
-  </si>
-  <si>
-    <t>136434239</t>
-  </si>
-  <si>
-    <t>136680957</t>
-  </si>
-  <si>
-    <t>133890056</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 10.02.2026</t>
+    <t>Relatório de Recusa SICOOB 11.02.2026</t>
+  </si>
+  <si>
+    <t>136490957</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 11.02.2026</t>
   </si>
 </sst>
 </file>
@@ -471,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -529,77 +517,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97864DC9-909D-4AA4-A9E7-D821A4F235AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E46057-6043-418A-8DB2-C4C675108B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,19 +51,28 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>132441027</t>
+    <t>136562068</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 11.02.2026</t>
-  </si>
-  <si>
-    <t>136490957</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 11.02.2026</t>
+    <t>Relatório de Recusa SICOOB 12.02.2026</t>
+  </si>
+  <si>
+    <t>136688168</t>
+  </si>
+  <si>
+    <t>136549834</t>
+  </si>
+  <si>
+    <t>136718359</t>
+  </si>
+  <si>
+    <t>136721282</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 12.02.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,9 +526,60 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1C13F-B151-42E7-B17A-010ECB910678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="48">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,129 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136450309</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 13.02.2026</t>
+  </si>
+  <si>
+    <t>136729415</t>
+  </si>
+  <si>
+    <t>136744748</t>
+  </si>
+  <si>
+    <t>136754471</t>
+  </si>
+  <si>
+    <t>136756405</t>
+  </si>
+  <si>
+    <t>136754869</t>
+  </si>
+  <si>
+    <t>136752480</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 13.02.2026</t>
+  </si>
+  <si>
+    <t>136578141</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 17.02.2026</t>
+  </si>
+  <si>
+    <t>136701200</t>
+  </si>
+  <si>
+    <t>136733513</t>
+  </si>
+  <si>
+    <t>136523313</t>
+  </si>
+  <si>
+    <t>136544687</t>
+  </si>
+  <si>
+    <t>136574829</t>
+  </si>
+  <si>
+    <t>136676059</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 17.02.2026</t>
+  </si>
+  <si>
+    <t>136506714</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 16.02.2026</t>
+  </si>
+  <si>
+    <t>136549693</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 16.02.2026</t>
+  </si>
+  <si>
+    <t>133890056</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 18.02.2026</t>
+  </si>
+  <si>
+    <t>136690230</t>
+  </si>
+  <si>
+    <t>136710215</t>
+  </si>
+  <si>
+    <t>136710099</t>
+  </si>
+  <si>
+    <t>136699735</t>
+  </si>
+  <si>
+    <t>136755999</t>
+  </si>
+  <si>
+    <t>136751030</t>
+  </si>
+  <si>
+    <t>136719470</t>
+  </si>
+  <si>
+    <t>136592135</t>
+  </si>
+  <si>
+    <t>136567750</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 18.02.2026</t>
+  </si>
+  <si>
+    <t>136350084</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 15.02.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 15.02.2026</t>
+  </si>
+  <si>
+    <t>136516475</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 14.02.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 14.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +598,478 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +1087,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88465112-CBED-42FF-83C2-F3809C0985FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,33 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136552267</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 19.02.2026</t>
+  </si>
+  <si>
+    <t>136603900</t>
+  </si>
+  <si>
+    <t>136606569</t>
+  </si>
+  <si>
+    <t>136566894</t>
+  </si>
+  <si>
+    <t>136746529</t>
+  </si>
+  <si>
+    <t>136803793</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 19.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +502,104 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +617,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00553F42-B8BF-4A9A-81E8-94EFFB1EA0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE8A016D-998F-4831-8D62-1767AE751724}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FD7C0-532C-4F34-A56B-24E48E0342CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,48 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136638867</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 23.02.2026</t>
+  </si>
+  <si>
+    <t>136683854</t>
+  </si>
+  <si>
+    <t>136696295</t>
+  </si>
+  <si>
+    <t>136702034</t>
+  </si>
+  <si>
+    <t>136831451</t>
+  </si>
+  <si>
+    <t>136745783</t>
+  </si>
+  <si>
+    <t>136753482</t>
+  </si>
+  <si>
+    <t>136754966</t>
+  </si>
+  <si>
+    <t>136759094</t>
+  </si>
+  <si>
+    <t>136760195</t>
+  </si>
+  <si>
+    <t>136760605</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 23.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,27 +517,189 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -513,31 +717,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797FD7C0-532C-4F34-A56B-24E48E0342CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3F8E08-444C-42F4-8473-7602B03825C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,53 +51,53 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136638867</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 23.02.2026</t>
-  </si>
-  <si>
-    <t>136683854</t>
-  </si>
-  <si>
-    <t>136696295</t>
-  </si>
-  <si>
-    <t>136702034</t>
-  </si>
-  <si>
-    <t>136831451</t>
-  </si>
-  <si>
-    <t>136745783</t>
-  </si>
-  <si>
-    <t>136753482</t>
-  </si>
-  <si>
-    <t>136754966</t>
-  </si>
-  <si>
-    <t>136759094</t>
-  </si>
-  <si>
-    <t>136760195</t>
-  </si>
-  <si>
-    <t>136760605</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 23.02.2026</t>
+    <t>Relatório de Recusa SICOOB 24.02.2026</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 24.02.2026</t>
+  </si>
+  <si>
+    <t>136838148</t>
+  </si>
+  <si>
+    <t>136838301</t>
+  </si>
+  <si>
+    <t>136837341</t>
+  </si>
+  <si>
+    <t>136839387</t>
+  </si>
+  <si>
+    <t>136734608</t>
+  </si>
+  <si>
+    <t>136667301</t>
+  </si>
+  <si>
+    <t>136718663</t>
+  </si>
+  <si>
+    <t>136718988</t>
+  </si>
+  <si>
+    <t>136854589</t>
+  </si>
+  <si>
+    <t>136865695</t>
+  </si>
+  <si>
+    <t>136751577</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +118,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -152,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -167,6 +173,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -486,7 +495,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -517,17 +526,17 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
+      <c r="A2" s="6">
+        <v>136837999</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -538,13 +547,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -555,13 +564,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -572,13 +581,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -589,13 +598,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -606,13 +615,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -623,13 +632,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -640,13 +649,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -657,13 +666,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -674,13 +683,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -691,15 +700,32 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3F8E08-444C-42F4-8473-7602B03825C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343A5C11-EF87-4DA0-A7A4-F2EBB2888502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,53 +51,44 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>136605244</t>
+  </si>
+  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 24.02.2026</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 24.02.2026</t>
-  </si>
-  <si>
-    <t>136838148</t>
-  </si>
-  <si>
-    <t>136838301</t>
-  </si>
-  <si>
-    <t>136837341</t>
-  </si>
-  <si>
-    <t>136839387</t>
-  </si>
-  <si>
-    <t>136734608</t>
-  </si>
-  <si>
-    <t>136667301</t>
-  </si>
-  <si>
-    <t>136718663</t>
-  </si>
-  <si>
-    <t>136718988</t>
-  </si>
-  <si>
-    <t>136854589</t>
-  </si>
-  <si>
-    <t>136865695</t>
-  </si>
-  <si>
-    <t>136751577</t>
+    <t>Relatório de Recusa SICOOB 25.02.2026</t>
+  </si>
+  <si>
+    <t>136731112</t>
+  </si>
+  <si>
+    <t>136722325</t>
+  </si>
+  <si>
+    <t>136886874</t>
+  </si>
+  <si>
+    <t>136889361</t>
+  </si>
+  <si>
+    <t>136821553</t>
+  </si>
+  <si>
+    <t>136831622</t>
+  </si>
+  <si>
+    <t>136827373</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 25.02.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,12 +109,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -158,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -173,9 +158,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -495,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -526,17 +508,17 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>136837999</v>
+      <c r="A2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -547,13 +529,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -564,13 +546,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -581,13 +563,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -598,13 +580,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -615,13 +597,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -632,13 +614,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -649,83 +631,15 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343A5C11-EF87-4DA0-A7A4-F2EBB2888502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230FFC43-312F-4F7D-853E-33190BC088EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,37 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136605244</t>
+    <t>Recusa Sicoob 26.02.2026</t>
+  </si>
+  <si>
+    <t>136762438</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 25.02.2026</t>
-  </si>
-  <si>
-    <t>136731112</t>
-  </si>
-  <si>
-    <t>136722325</t>
-  </si>
-  <si>
-    <t>136886874</t>
-  </si>
-  <si>
-    <t>136889361</t>
-  </si>
-  <si>
-    <t>136821553</t>
-  </si>
-  <si>
-    <t>136831622</t>
-  </si>
-  <si>
-    <t>136827373</t>
-  </si>
-  <si>
-    <t>Recusa Sicoob 25.02.2026</t>
+    <t>Relatório de Recusa SICOOB 26.02.2026</t>
+  </si>
+  <si>
+    <t>136809497</t>
+  </si>
+  <si>
+    <t>136804375</t>
   </si>
 </sst>
 </file>
@@ -477,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,16 +494,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,16 +511,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -543,103 +528,18 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFGRECUSA_SICOOB_MINASEG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230FFC43-312F-4F7D-853E-33190BC088EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D362F8-6E11-4E4C-A4D9-E527110FBCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,34 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusa Sicoob 26.02.2026</t>
-  </si>
-  <si>
-    <t>136762438</t>
+    <t>136894775</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa SICOOB 26.02.2026</t>
-  </si>
-  <si>
-    <t>136809497</t>
-  </si>
-  <si>
-    <t>136804375</t>
+    <t>Relatório de Recusa SICOOB 27.02.2026</t>
+  </si>
+  <si>
+    <t>132383991</t>
+  </si>
+  <si>
+    <t>136927244</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 27.02.2026</t>
+  </si>
+  <si>
+    <t>136918232</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa SICOOB 28.02.2026</t>
+  </si>
+  <si>
+    <t>136893813</t>
+  </si>
+  <si>
+    <t>Recusa Sicoob 28.02.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -494,16 +506,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -511,16 +523,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -528,18 +540,52 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -557,31 +603,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>